--- a/order_generation/PO_excel_export/factory-3.xlsx
+++ b/order_generation/PO_excel_export/factory-3.xlsx
@@ -358,6 +358,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1581150" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -785,7 +810,11 @@
           <t>电话：</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>0574-27889688</t>
+        </is>
+      </c>
       <c r="C4" s="16" t="n"/>
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
@@ -807,7 +836,11 @@
           <t>联系人：</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>XX印刷厂</t>
+        </is>
+      </c>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -886,14 +919,33 @@
       <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
       <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>15*20黑色棘皮绒单面，黑色棉绳，双色logo，N字母烫金</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>散货</t>
+        </is>
+      </c>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
